--- a/freTMPL2/Relatividades_MTPL.xlsx
+++ b/freTMPL2/Relatividades_MTPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,19 @@
         <v>1.204377587164353</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E[Sev]</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2401.748576812059</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2401.748576812059</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
